--- a/data/trans_camb/P1432-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1432-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,04</t>
+          <t>-2,04; 0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,44</t>
+          <t>-1,88; 0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,82</t>
+          <t>-0,25; 2,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,1</t>
+          <t>-0,48; 1,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,61</t>
+          <t>-1,06; 0,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,64</t>
+          <t>-1,06; 0,63</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,8; 329,72</t>
+          <t>-97,39; 297,69</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,01</t>
+          <t>-2,49; -0,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,25</t>
+          <t>-2,26; 0,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,17</t>
+          <t>-1,35; 2,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; -0,36</t>
+          <t>-2,08; -0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,87</t>
+          <t>-1,41; 0,8</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 123,41</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 616,0</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -2,76</t>
+          <t>-100,0; 1,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 173,78</t>
+          <t>-80,55; 129,4</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,5</t>
+          <t>-1,13; 1,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,62</t>
+          <t>-1,62; 0,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,57</t>
+          <t>-2,96; 1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,89</t>
+          <t>-2,76; 2,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,15</t>
+          <t>-1,13; 1,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,78</t>
+          <t>-1,45; 0,76</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,95; 388,1</t>
+          <t>-72,58; 320,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 181,33</t>
+          <t>-100,0; 343,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 183,81</t>
+          <t>-67,51; 199,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,48; 148,62</t>
+          <t>-81,84; 158,14</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,55</t>
+          <t>-1,27; 0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; -0,3</t>
+          <t>-1,65; -0,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,66</t>
+          <t>-1,07; 0,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,39</t>
+          <t>-0,76; 1,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,32</t>
+          <t>-0,95; 0,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,12</t>
+          <t>-1,07; 0,13</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 73,02</t>
+          <t>-75,94; 53,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,88; -21,83</t>
+          <t>-90,14; -17,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,47; 202,49</t>
+          <t>-82,5; 221,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,9; 385,58</t>
+          <t>-62,07; 381,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 39,77</t>
+          <t>-66,47; 47,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 18,29</t>
+          <t>-70,25; 23,74</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,43</t>
+          <t>-2,39; 0,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,81</t>
+          <t>-1,83; 0,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,56</t>
+          <t>-0,89; 2,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,27</t>
+          <t>-2,51; 0,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,34</t>
+          <t>-1,08; 1,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,25</t>
+          <t>-1,97; 0,07</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,7</t>
+          <t>-100,0; 134,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,43; 174,76</t>
+          <t>-81,0; 200,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 271,78</t>
+          <t>-31,43; 206,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-86,6; 35,59</t>
+          <t>-81,87; 47,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 120,94</t>
+          <t>-45,14; 118,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,86; 27,03</t>
+          <t>-76,15; 12,74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,59</t>
+          <t>-1,14; 1,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,55</t>
+          <t>-1,03; 1,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,21</t>
+          <t>-0,92; 1,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,18</t>
+          <t>-0,9; 1,12</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-39,87; 101,47</t>
+          <t>-44,36; 97,49</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 107,78</t>
+          <t>-40,33; 97,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,53; 103,79</t>
+          <t>-40,44; 92,67</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-41,19; 101,44</t>
+          <t>-41,93; 94,08</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,02</t>
+          <t>-0,96; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; -0,17</t>
+          <t>-1,03; -0,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,75</t>
+          <t>-0,49; 0,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,61</t>
+          <t>-0,7; 0,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,23</t>
+          <t>-0,56; 0,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,08</t>
+          <t>-0,74; 0,04</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 2,47</t>
+          <t>-69,47; 4,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,11; -16,44</t>
+          <t>-72,75; -14,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 66,83</t>
+          <t>-27,48; 62,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 55,01</t>
+          <t>-39,28; 44,36</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 21,12</t>
+          <t>-36,61; 20,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 8,35</t>
+          <t>-47,72; 3,7</t>
         </is>
       </c>
     </row>
